--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCFE2A3-7914-42CD-9CB7-0D2DC6207E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5314EE24-5E78-4511-88DD-AEC50203A95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="163">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -51,9 +51,6 @@
     <t>313: {"Zozo": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},   # Zozo WoB Ramuh reward</t>
   </si>
   <si>
-    <t>229: {"Mobliz WOR": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},   # Mobliz WoR.  Actually '237R' if interiors randomized.</t>
-  </si>
-  <si>
     <t>34: {"Narshe WOR": [RewardType.ESPER, RewardType.ITEM]},   # Narshe WOR weapon shop.  Actually '25R' if interiors are randomized.</t>
   </si>
   <si>
@@ -514,6 +511,21 @@
   </si>
   <si>
     <t xml:space="preserve">Removed.  It should just work as an ungated entrance, too confusing otherwise.  </t>
+  </si>
+  <si>
+    <t>Arvis showing in WoR Narshe?</t>
+  </si>
+  <si>
+    <t>ruin-narshe</t>
+  </si>
+  <si>
+    <t>Changed init event bit in moogle_defense.py</t>
+  </si>
+  <si>
+    <t>ms-wor-52</t>
+  </si>
+  <si>
+    <t>ms-wor-52': {"Mobliz WOR": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},   # Mobliz WoR.  Actually '237R' if interiors randomized.</t>
   </si>
 </sst>
 </file>
@@ -584,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -594,6 +606,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -944,61 +957,70 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" t="s">
-        <v>48</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E6" s="4">
         <v>313</v>
@@ -1008,603 +1030,720 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="4">
-        <v>229</v>
-      </c>
-      <c r="F7" t="s">
-        <v>4</v>
+        <v>57</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" s="4">
         <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
         <v>60</v>
-      </c>
-      <c r="D9" t="s">
-        <v>61</v>
       </c>
       <c r="E9" s="4">
         <v>104</v>
       </c>
       <c r="F9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E10" s="4">
         <v>537</v>
       </c>
       <c r="F10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C11" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="s">
         <v>67</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" t="s">
-        <v>68</v>
       </c>
       <c r="E13" s="4">
         <v>532</v>
       </c>
       <c r="F13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
         <v>73</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" t="s">
-        <v>74</v>
       </c>
       <c r="E16" s="4">
         <v>220</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E17" s="4">
         <v>151</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E18" s="4">
         <v>395</v>
       </c>
       <c r="F18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C19" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" t="s">
         <v>80</v>
-      </c>
-      <c r="D19" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" t="s">
-        <v>81</v>
       </c>
       <c r="E21" s="4">
         <v>349</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" s="4">
         <v>354</v>
       </c>
       <c r="F22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C23" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C24" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" t="s">
         <v>87</v>
-      </c>
-      <c r="D24" t="s">
-        <v>88</v>
       </c>
       <c r="E24" s="4">
         <v>429</v>
       </c>
       <c r="F24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E25" s="4">
         <v>193</v>
       </c>
       <c r="F25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C26" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" t="s">
         <v>90</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C27" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" t="s">
-        <v>91</v>
       </c>
       <c r="E27" s="4">
         <v>256</v>
       </c>
       <c r="F27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C28" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" t="s">
         <v>95</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F29" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E30" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" t="s">
         <v>93</v>
       </c>
-      <c r="F29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>97</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E31" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" t="s">
         <v>93</v>
       </c>
-      <c r="F30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C31" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>98</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F31" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C32" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" t="s">
-        <v>99</v>
       </c>
       <c r="E32" s="4">
         <v>475</v>
       </c>
       <c r="F32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F33" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C33" t="s">
-        <v>100</v>
-      </c>
-      <c r="D33" t="s">
-        <v>104</v>
-      </c>
-      <c r="E33" s="4" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F34" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C34" t="s">
-        <v>100</v>
-      </c>
-      <c r="D34" t="s">
-        <v>103</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F34" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D36" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" t="s">
         <v>109</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="D37" t="s">
+        <v>110</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C37" t="s">
-        <v>110</v>
-      </c>
-      <c r="D37" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" t="s">
         <v>111</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E38" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F38" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C38" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" t="s">
         <v>112</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E39" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C39" t="s">
-        <v>110</v>
-      </c>
-      <c r="D39" t="s">
-        <v>113</v>
-      </c>
-      <c r="E39" s="4" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" t="s">
         <v>116</v>
       </c>
-      <c r="F39" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>117</v>
-      </c>
-      <c r="D40" t="s">
-        <v>118</v>
       </c>
       <c r="E40" s="4">
         <v>488</v>
       </c>
       <c r="F40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D41" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E41" s="4">
         <v>284</v>
       </c>
       <c r="F41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C42" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E42" s="4">
         <v>23</v>
       </c>
       <c r="F42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C43" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" t="s">
         <v>120</v>
-      </c>
-      <c r="D43" t="s">
-        <v>121</v>
       </c>
       <c r="E43" s="4">
         <v>65</v>
       </c>
       <c r="F43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C44" t="s">
+        <v>122</v>
+      </c>
+      <c r="D44" t="s">
         <v>123</v>
-      </c>
-      <c r="D44" t="s">
-        <v>124</v>
       </c>
       <c r="E44" s="4">
         <v>368</v>
       </c>
       <c r="F44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C45" t="s">
+        <v>124</v>
+      </c>
+      <c r="D45" t="s">
         <v>125</v>
-      </c>
-      <c r="D45" t="s">
-        <v>126</v>
       </c>
       <c r="E45" s="4">
         <v>363</v>
       </c>
       <c r="F45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F46" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C46" t="s">
-        <v>127</v>
-      </c>
-      <c r="D46" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" t="s">
         <v>131</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F47" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C47" t="s">
-        <v>127</v>
-      </c>
-      <c r="D47" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" t="s">
+        <v>126</v>
+      </c>
+      <c r="D48" t="s">
         <v>132</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E48" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F48" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C48" t="s">
-        <v>127</v>
-      </c>
-      <c r="D48" t="s">
-        <v>133</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="F48" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1614,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C8A44C-B798-4416-9AA8-07AAF9D050FB}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" style="1" customWidth="1"/>
@@ -1624,7 +1763,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E1" s="4"/>
     </row>
@@ -1633,170 +1772,184 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" t="s">
         <v>136</v>
-      </c>
-      <c r="D4" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G11" t="s">
         <v>157</v>
-      </c>
-      <c r="G11" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G14" t="s">
-        <v>150</v>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5314EE24-5E78-4511-88DD-AEC50203A95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FE585B-B5DA-44A5-8200-5E7F8787636F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="166">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -526,6 +526,15 @@
   </si>
   <si>
     <t>ms-wor-52': {"Mobliz WOR": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},   # Mobliz WoR.  Actually '237R' if interiors randomized.</t>
+  </si>
+  <si>
+    <t>Always show Sealed Gate trap exit</t>
+  </si>
+  <si>
+    <t>edit in sealed_gate.ruination_mod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party formation after Phunbaba is broken!  </t>
   </si>
 </sst>
 </file>
@@ -941,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93C4B77-39C0-44C7-B9BF-61991AECD056}">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
@@ -950,12 +959,12 @@
     <col min="5" max="5" width="11.54296875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>46</v>
       </c>
@@ -972,10 +981,13 @@
         <v>51</v>
       </c>
       <c r="F3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>56</v>
       </c>
@@ -991,11 +1003,11 @@
       <c r="E4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>56</v>
       </c>
@@ -1008,12 +1020,15 @@
       <c r="E5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F5" t="s">
+      <c r="J5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>56</v>
       </c>
       <c r="C6" t="s">
@@ -1025,11 +1040,11 @@
       <c r="E6" s="4">
         <v>313</v>
       </c>
-      <c r="F6" t="s">
+      <c r="J6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>56</v>
       </c>
@@ -1042,11 +1057,14 @@
       <c r="E7" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>56</v>
       </c>
@@ -1059,11 +1077,11 @@
       <c r="E8" s="4">
         <v>34</v>
       </c>
-      <c r="F8" t="s">
+      <c r="J8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>56</v>
       </c>
@@ -1076,11 +1094,11 @@
       <c r="E9" s="4">
         <v>104</v>
       </c>
-      <c r="F9" t="s">
+      <c r="J9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
         <v>59</v>
       </c>
@@ -1090,11 +1108,11 @@
       <c r="E10" s="4">
         <v>537</v>
       </c>
-      <c r="F10" t="s">
+      <c r="J10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>56</v>
       </c>
@@ -1107,11 +1125,11 @@
       <c r="E11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F11" t="s">
+      <c r="J11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>56</v>
       </c>
@@ -1124,11 +1142,11 @@
       <c r="E12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F12" t="s">
+      <c r="J12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>56</v>
       </c>
@@ -1141,11 +1159,11 @@
       <c r="E13" s="4">
         <v>532</v>
       </c>
-      <c r="F13" t="s">
+      <c r="J13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>56</v>
       </c>
@@ -1158,11 +1176,11 @@
       <c r="E14" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F14" t="s">
+      <c r="J14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>56</v>
       </c>
@@ -1175,11 +1193,11 @@
       <c r="E15" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F15" t="s">
+      <c r="J15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>56</v>
       </c>
@@ -1192,11 +1210,11 @@
       <c r="E16" s="4">
         <v>220</v>
       </c>
-      <c r="F16" t="s">
+      <c r="J16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
@@ -1209,11 +1227,11 @@
       <c r="E17" s="4">
         <v>151</v>
       </c>
-      <c r="F17" t="s">
+      <c r="J17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
@@ -1226,11 +1244,11 @@
       <c r="E18" s="4">
         <v>395</v>
       </c>
-      <c r="F18" t="s">
+      <c r="J18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>56</v>
       </c>
@@ -1243,11 +1261,11 @@
       <c r="E19" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F19" t="s">
+      <c r="J19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>56</v>
       </c>
@@ -1260,11 +1278,11 @@
       <c r="E20" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F20" t="s">
+      <c r="J20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>56</v>
       </c>
@@ -1277,11 +1295,11 @@
       <c r="E21" s="4">
         <v>349</v>
       </c>
-      <c r="F21" t="s">
+      <c r="J21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>56</v>
       </c>
@@ -1294,11 +1312,11 @@
       <c r="E22" s="4">
         <v>354</v>
       </c>
-      <c r="F22" t="s">
+      <c r="J22" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>56</v>
       </c>
@@ -1311,11 +1329,11 @@
       <c r="E23" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F23" t="s">
+      <c r="J23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>56</v>
       </c>
@@ -1328,11 +1346,11 @@
       <c r="E24" s="4">
         <v>429</v>
       </c>
-      <c r="F24" t="s">
+      <c r="J24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>56</v>
       </c>
@@ -1345,11 +1363,11 @@
       <c r="E25" s="4">
         <v>193</v>
       </c>
-      <c r="F25" t="s">
+      <c r="J25" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -1362,11 +1380,11 @@
       <c r="E26" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F26" t="s">
+      <c r="J26" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>56</v>
       </c>
@@ -1379,11 +1397,11 @@
       <c r="E27" s="4">
         <v>256</v>
       </c>
-      <c r="F27" t="s">
+      <c r="J27" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>56</v>
       </c>
@@ -1396,11 +1414,11 @@
       <c r="E28" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F28" t="s">
+      <c r="J28" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>56</v>
       </c>
@@ -1413,11 +1431,11 @@
       <c r="E29" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F29" t="s">
+      <c r="J29" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>56</v>
       </c>
@@ -1430,11 +1448,11 @@
       <c r="E30" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F30" t="s">
+      <c r="J30" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>56</v>
       </c>
@@ -1447,11 +1465,11 @@
       <c r="E31" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F31" t="s">
+      <c r="J31" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>56</v>
       </c>
@@ -1464,11 +1482,11 @@
       <c r="E32" s="4">
         <v>475</v>
       </c>
-      <c r="F32" t="s">
+      <c r="J32" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>56</v>
       </c>
@@ -1481,11 +1499,11 @@
       <c r="E33" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F33" t="s">
+      <c r="J33" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>56</v>
       </c>
@@ -1498,11 +1516,11 @@
       <c r="E34" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F34" t="s">
+      <c r="J34" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>56</v>
       </c>
@@ -1518,11 +1536,11 @@
       <c r="E35" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F35" t="s">
+      <c r="J35" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>56</v>
       </c>
@@ -1538,11 +1556,11 @@
       <c r="E36" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F36" t="s">
+      <c r="J36" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>56</v>
       </c>
@@ -1555,11 +1573,11 @@
       <c r="E37" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F37" t="s">
+      <c r="J37" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>56</v>
       </c>
@@ -1572,11 +1590,11 @@
       <c r="E38" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F38" t="s">
+      <c r="J38" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>56</v>
       </c>
@@ -1589,11 +1607,11 @@
       <c r="E39" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F39" t="s">
+      <c r="J39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>56</v>
       </c>
@@ -1606,11 +1624,11 @@
       <c r="E40" s="4">
         <v>488</v>
       </c>
-      <c r="F40" t="s">
+      <c r="J40" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>56</v>
       </c>
@@ -1623,11 +1641,11 @@
       <c r="E41" s="4">
         <v>284</v>
       </c>
-      <c r="F41" t="s">
+      <c r="J41" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>56</v>
       </c>
@@ -1640,11 +1658,11 @@
       <c r="E42" s="4">
         <v>23</v>
       </c>
-      <c r="F42" t="s">
+      <c r="J42" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>56</v>
       </c>
@@ -1657,11 +1675,11 @@
       <c r="E43" s="4">
         <v>65</v>
       </c>
-      <c r="F43" t="s">
+      <c r="J43" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>56</v>
       </c>
@@ -1674,11 +1692,11 @@
       <c r="E44" s="4">
         <v>368</v>
       </c>
-      <c r="F44" t="s">
+      <c r="J44" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>56</v>
       </c>
@@ -1691,11 +1709,11 @@
       <c r="E45" s="4">
         <v>363</v>
       </c>
-      <c r="F45" t="s">
+      <c r="J45" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>56</v>
       </c>
@@ -1708,11 +1726,11 @@
       <c r="E46" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F46" t="s">
+      <c r="J46" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>56</v>
       </c>
@@ -1725,11 +1743,11 @@
       <c r="E47" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F47" t="s">
+      <c r="J47" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>56</v>
       </c>
@@ -1742,7 +1760,7 @@
       <c r="E48" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F48" t="s">
+      <c r="J48" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1753,12 +1771,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C8A44C-B798-4416-9AA8-07AAF9D050FB}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.7265625" style="5"/>
-    <col min="3" max="3" width="16.08984375" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -1794,7 +1812,7 @@
       <c r="B4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>135</v>
       </c>
       <c r="D4" t="s">
@@ -1808,7 +1826,7 @@
       <c r="B5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>135</v>
       </c>
       <c r="D5" t="s">
@@ -1822,7 +1840,7 @@
       <c r="B6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>150</v>
       </c>
       <c r="D6" t="s">
@@ -1836,7 +1854,7 @@
       <c r="B7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>151</v>
       </c>
       <c r="D7" t="s">
@@ -1850,7 +1868,7 @@
       <c r="B8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>152</v>
       </c>
       <c r="D8" t="s">
@@ -1875,7 +1893,7 @@
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>141</v>
       </c>
       <c r="D10" t="s">
@@ -1886,7 +1904,7 @@
       <c r="A11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="6" t="s">
@@ -1900,7 +1918,7 @@
       <c r="A12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="4" t="s">
         <v>142</v>
       </c>
       <c r="D12" t="s">
@@ -1914,7 +1932,7 @@
       <c r="A13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="4" t="s">
         <v>145</v>
       </c>
       <c r="D13" t="s">
@@ -1928,7 +1946,7 @@
       <c r="A14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="4" t="s">
         <v>142</v>
       </c>
       <c r="D14" t="s">
@@ -1942,7 +1960,7 @@
       <c r="A15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="4" t="s">
         <v>159</v>
       </c>
       <c r="D15" t="s">
@@ -1950,6 +1968,20 @@
       </c>
       <c r="G15" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="4">
+        <v>507</v>
+      </c>
+      <c r="D16" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FE585B-B5DA-44A5-8200-5E7F8787636F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91136B0C-8C9B-40EA-B552-EBB3257AC0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="167">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -535,13 +535,16 @@
   </si>
   <si>
     <t xml:space="preserve">Party formation after Phunbaba is broken!  </t>
+  </si>
+  <si>
+    <t>NOTE: ALL PLAYTESTING THAT INVOLVES PARTY FORMATION MUST BE DONE WITH BOTH PARTY1 and either PARTY 2 or 3!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -584,6 +587,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -605,7 +616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -616,6 +627,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -963,6 +975,9 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -991,8 +1006,8 @@
       <c r="A4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>56</v>
+      <c r="B4" s="3">
+        <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>55</v>
@@ -1028,8 +1043,8 @@
       <c r="A6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
+      <c r="B6" s="3">
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>55</v>
@@ -1524,8 +1539,8 @@
       <c r="A35" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>56</v>
+      <c r="B35" s="3">
+        <v>1</v>
       </c>
       <c r="C35" t="s">
         <v>104</v>
@@ -1544,8 +1559,8 @@
       <c r="A36" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>56</v>
+      <c r="B36" s="3">
+        <v>1</v>
       </c>
       <c r="C36" t="s">
         <v>104</v>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91136B0C-8C9B-40EA-B552-EBB3257AC0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0AA8BB6-3D80-451F-A22B-0249657EB27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="170">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -51,15 +51,9 @@
     <t>313: {"Zozo": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},   # Zozo WoB Ramuh reward</t>
   </si>
   <si>
-    <t>34: {"Narshe WOR": [RewardType.ESPER, RewardType.ITEM]},   # Narshe WOR weapon shop.  Actually '25R' if interiors are randomized.</t>
-  </si>
-  <si>
     <t>104: {"South Figaro Cave": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # TunnelArmr spot</t>
   </si>
   <si>
-    <t>537: {"Phoenix Cave": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Phoenix Cave (interior 1st room).  For outside platform: 'branch-pc'.  Need to modify exit: warp to esper world?</t>
-  </si>
-  <si>
     <t>'ruin-figarocastle': {"Figaro Castle WOB": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM],</t>
   </si>
   <si>
@@ -534,10 +528,25 @@
     <t>edit in sealed_gate.ruination_mod</t>
   </si>
   <si>
-    <t xml:space="preserve">Party formation after Phunbaba is broken!  </t>
-  </si>
-  <si>
     <t>NOTE: ALL PLAYTESTING THAT INVOLVES PARTY FORMATION MUST BE DONE WITH BOTH PARTY1 and either PARTY 2 or 3!</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Party walks at slow speed for some reason</t>
+  </si>
+  <si>
+    <t>Remove Gogo character gating bridge troll block (part of "no nonlocal character gating")</t>
+  </si>
+  <si>
+    <t>ms-wor-1554</t>
+  </si>
+  <si>
+    <t>ms-wor-1554': {"Phoenix Cave": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Phoenix Cave (interior 1st room).  For outside platform: 'branch-pc'.  Need to modify exit: warp to esper world?</t>
+  </si>
+  <si>
+    <t>ruin-narshe': {"Narshe WOR": [RewardType.ESPER, RewardType.ITEM]},   # Narshe WOR weapon shop.  Actually '25R' if interiors are randomized.</t>
   </si>
 </sst>
 </file>
@@ -976,47 +985,47 @@
         <v>0</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
         <v>45</v>
       </c>
-      <c r="C3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" t="s">
-        <v>47</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="3">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J4" t="s">
         <v>1</v>
@@ -1024,16 +1033,19 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J5" t="s">
         <v>2</v>
@@ -1041,16 +1053,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E6" s="4">
         <v>313</v>
@@ -1061,722 +1073,723 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
         <v>55</v>
       </c>
-      <c r="D7" t="s">
-        <v>57</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>165</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="F7" s="1"/>
       <c r="J7" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="4">
-        <v>34</v>
-      </c>
-      <c r="J8" t="s">
-        <v>4</v>
+        <v>60</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E9" s="4">
         <v>104</v>
       </c>
       <c r="J9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
         <v>59</v>
       </c>
-      <c r="D10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="4">
-        <v>537</v>
-      </c>
-      <c r="J10" t="s">
-        <v>6</v>
+      <c r="E10" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
         <v>63</v>
       </c>
-      <c r="D12" t="s">
-        <v>65</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E13" s="4">
         <v>532</v>
       </c>
       <c r="J13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="J15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E16" s="4">
         <v>220</v>
       </c>
       <c r="J16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E17" s="4">
         <v>151</v>
       </c>
       <c r="J17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E18" s="4">
         <v>395</v>
       </c>
       <c r="J18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E21" s="4">
         <v>349</v>
       </c>
       <c r="J21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" t="s">
         <v>79</v>
-      </c>
-      <c r="D22" t="s">
-        <v>81</v>
       </c>
       <c r="E22" s="4">
         <v>354</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E24" s="4">
         <v>429</v>
       </c>
       <c r="J24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" t="s">
         <v>86</v>
-      </c>
-      <c r="D25" t="s">
-        <v>88</v>
       </c>
       <c r="E25" s="4">
         <v>193</v>
       </c>
       <c r="J25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E27" s="4">
         <v>256</v>
       </c>
       <c r="J27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" t="s">
         <v>93</v>
       </c>
-      <c r="D29" t="s">
-        <v>95</v>
-      </c>
       <c r="E29" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J30" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E32" s="4">
         <v>475</v>
       </c>
       <c r="J32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J33" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
+        <v>97</v>
+      </c>
+      <c r="D34" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D34" t="s">
-        <v>102</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="J34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B35" s="3">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J35" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B36" s="3">
         <v>1</v>
       </c>
       <c r="C36" t="s">
+        <v>102</v>
+      </c>
+      <c r="D36" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D36" t="s">
-        <v>108</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="J36" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J37" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" t="s">
         <v>109</v>
       </c>
-      <c r="D38" t="s">
-        <v>111</v>
-      </c>
       <c r="E38" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D39" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J39" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D40" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E40" s="4">
         <v>488</v>
       </c>
       <c r="J40" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" t="s">
         <v>116</v>
-      </c>
-      <c r="D41" t="s">
-        <v>118</v>
       </c>
       <c r="E41" s="4">
         <v>284</v>
       </c>
       <c r="J41" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
+        <v>117</v>
+      </c>
+      <c r="D42" t="s">
         <v>119</v>
-      </c>
-      <c r="D42" t="s">
-        <v>121</v>
       </c>
       <c r="E42" s="4">
         <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D43" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E43" s="4">
         <v>65</v>
       </c>
       <c r="J43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D44" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E44" s="4">
         <v>368</v>
       </c>
       <c r="J44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D45" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E45" s="4">
         <v>363</v>
       </c>
       <c r="J45" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D46" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J46" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
+        <v>124</v>
+      </c>
+      <c r="D47" t="s">
+        <v>129</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D47" t="s">
-        <v>131</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>128</v>
-      </c>
       <c r="J47" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D48" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J48" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1786,7 +1799,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C8A44C-B798-4416-9AA8-07AAF9D050FB}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" style="1" customWidth="1"/>
@@ -1796,7 +1809,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E1" s="4"/>
     </row>
@@ -1805,198 +1818,218 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" t="s">
         <v>135</v>
-      </c>
-      <c r="D5" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>137</v>
+      </c>
+      <c r="G10" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" t="s">
         <v>142</v>
       </c>
-      <c r="D14" t="s">
-        <v>144</v>
-      </c>
       <c r="G14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
+        <v>156</v>
+      </c>
+      <c r="G15" t="s">
         <v>158</v>
-      </c>
-      <c r="G15" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C16" s="4">
         <v>507</v>
       </c>
       <c r="D16" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G16" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>164</v>
+      </c>
+      <c r="C17" s="4">
+        <v>114</v>
+      </c>
+      <c r="D17" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0AA8BB6-3D80-451F-A22B-0249657EB27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C260FEA-87A4-4D04-B244-1EC735544C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="19200" windowHeight="11170" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C260FEA-87A4-4D04-B244-1EC735544C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0786478-C27B-4ABF-843B-DEEFFB17DC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3000" windowWidth="19200" windowHeight="11170" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="172">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -87,9 +87,6 @@
     <t>349: {"Magitek Factory_1": [RewardType.ESPER, RewardType.ITEM]},  # Magitek Factory 1</t>
   </si>
   <si>
-    <t>354: {"Magitek Factory_2": [RewardType.ESPER, RewardType.ITEM]},  # Magitek Factory 2</t>
-  </si>
-  <si>
     <t>'ruin-mtek3': {"Magitek Factory_3": [RewardType.CHARACTER, RewardType.ESPER]},  # Magitek Factory 3, needs logical separation from Vector.  2nd boss where?</t>
   </si>
   <si>
@@ -547,13 +544,22 @@
   </si>
   <si>
     <t>ruin-narshe': {"Narshe WOR": [RewardType.ESPER, RewardType.ITEM]},   # Narshe WOR weapon shop.  Actually '25R' if interiors are randomized.</t>
+  </si>
+  <si>
+    <t>ruin-mtek2</t>
+  </si>
+  <si>
+    <t>ruin-mtek2: {"Magitek Factory_2": [RewardType.ESPER, RewardType.ITEM]},  # Magitek Factory 2</t>
+  </si>
+  <si>
+    <t>Rare interaction!   Cyan's Dream Mtek --&gt; Mtek3 exit after already completed, Mtek armor is not cleared.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -604,6 +610,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -625,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -637,6 +652,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -985,47 +1001,47 @@
         <v>0</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" t="s">
-        <v>45</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>164</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J4" t="s">
         <v>1</v>
@@ -1033,19 +1049,19 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J5" t="s">
         <v>2</v>
@@ -1053,16 +1069,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>164</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6" s="4">
         <v>313</v>
@@ -1073,51 +1089,57 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" t="s">
-        <v>55</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F7" s="1"/>
       <c r="J7" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
         <v>57</v>
-      </c>
-      <c r="D9" t="s">
-        <v>58</v>
       </c>
       <c r="E9" s="4">
         <v>104</v>
@@ -1127,31 +1149,37 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>163</v>
+      </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="D11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="J11" t="s">
         <v>5</v>
@@ -1159,16 +1187,16 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="D12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="J12" t="s">
         <v>6</v>
@@ -1176,13 +1204,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" s="4">
         <v>532</v>
@@ -1193,16 +1221,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="D14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="J14" t="s">
         <v>8</v>
@@ -1210,16 +1238,16 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J15" t="s">
         <v>9</v>
@@ -1227,13 +1255,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" s="4">
         <v>220</v>
@@ -1244,13 +1272,13 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" s="4">
         <v>151</v>
@@ -1261,13 +1289,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E18" s="4">
         <v>395</v>
@@ -1278,16 +1306,19 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J19" t="s">
         <v>13</v>
@@ -1295,16 +1326,19 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J20" t="s">
         <v>14</v>
@@ -1312,13 +1346,16 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
         <v>77</v>
-      </c>
-      <c r="D21" t="s">
-        <v>78</v>
       </c>
       <c r="E21" s="4">
         <v>349</v>
@@ -1329,467 +1366,476 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="4">
-        <v>354</v>
+        <v>78</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>169</v>
       </c>
       <c r="J22" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="J23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" t="s">
         <v>84</v>
-      </c>
-      <c r="D24" t="s">
-        <v>85</v>
       </c>
       <c r="E24" s="4">
         <v>429</v>
       </c>
       <c r="J24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25" s="4">
         <v>193</v>
       </c>
       <c r="J25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E27" s="4">
         <v>256</v>
       </c>
       <c r="J27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" t="s">
         <v>91</v>
       </c>
-      <c r="D28" t="s">
-        <v>92</v>
-      </c>
       <c r="E28" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E32" s="4">
         <v>475</v>
       </c>
       <c r="J32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D33" t="s">
-        <v>101</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>98</v>
-      </c>
       <c r="J33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="3">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="C35" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" t="s">
+        <v>104</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D35" t="s">
-        <v>105</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>103</v>
-      </c>
       <c r="J35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" s="3">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D36" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" t="s">
         <v>107</v>
       </c>
-      <c r="D37" t="s">
-        <v>108</v>
-      </c>
       <c r="E37" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D39" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" t="s">
         <v>114</v>
-      </c>
-      <c r="D40" t="s">
-        <v>115</v>
       </c>
       <c r="E40" s="4">
         <v>488</v>
       </c>
       <c r="J40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D41" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E41" s="4">
         <v>284</v>
       </c>
       <c r="J41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E42" s="4">
         <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" t="s">
         <v>117</v>
-      </c>
-      <c r="D43" t="s">
-        <v>118</v>
       </c>
       <c r="E43" s="4">
         <v>65</v>
       </c>
       <c r="J43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
+        <v>119</v>
+      </c>
+      <c r="D44" t="s">
         <v>120</v>
-      </c>
-      <c r="D44" t="s">
-        <v>121</v>
       </c>
       <c r="E44" s="4">
         <v>368</v>
       </c>
       <c r="J44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" t="s">
         <v>122</v>
-      </c>
-      <c r="D45" t="s">
-        <v>123</v>
       </c>
       <c r="E45" s="4">
         <v>363</v>
       </c>
       <c r="J45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" t="s">
+        <v>123</v>
+      </c>
+      <c r="D46" t="s">
+        <v>127</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D46" t="s">
-        <v>128</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="J46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D48" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1809,7 +1855,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E1" s="4"/>
     </row>
@@ -1818,218 +1864,218 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" t="s">
         <v>133</v>
-      </c>
-      <c r="D4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" t="s">
         <v>164</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D10" t="s">
-        <v>137</v>
-      </c>
-      <c r="G10" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G11" t="s">
         <v>154</v>
-      </c>
-      <c r="G11" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" t="s">
+        <v>155</v>
+      </c>
+      <c r="G15" t="s">
         <v>157</v>
-      </c>
-      <c r="D15" t="s">
-        <v>156</v>
-      </c>
-      <c r="G15" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="4">
         <v>507</v>
       </c>
       <c r="D16" t="s">
+        <v>160</v>
+      </c>
+      <c r="G16" t="s">
         <v>161</v>
-      </c>
-      <c r="G16" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C17" s="4">
         <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0786478-C27B-4ABF-843B-DEEFFB17DC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF4522E-8A16-4588-9E3B-A029E9CC41CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="19200" windowHeight="11170" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="172">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -1189,6 +1189,9 @@
       <c r="A12" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="B12" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="C12" t="s">
         <v>60</v>
       </c>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF4522E-8A16-4588-9E3B-A029E9CC41CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A44EF6F-8515-4DBC-8DF7-E53DC2C2FB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3000" windowWidth="19200" windowHeight="11170" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="174">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -75,9 +75,6 @@
     <t>151: {"Mt. Kolts": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Mt Kolts</t>
   </si>
   <si>
-    <t>395: {"Collapsing House": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Tzen WoR Collapsing house</t>
-  </si>
-  <si>
     <t>'ms-wor-58': {"South Figaro": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # South Figaro Basement  World of Ruin;  WOB is 'ms-wob-6'.</t>
   </si>
   <si>
@@ -553,6 +550,15 @@
   </si>
   <si>
     <t>Rare interaction!   Cyan's Dream Mtek --&gt; Mtek3 exit after already completed, Mtek armor is not cleared.</t>
+  </si>
+  <si>
+    <t>If you recruit a character on phantom train into the local party, then y-cycle back to the party, the character is still walking around &amp; you can recruit them again.</t>
+  </si>
+  <si>
+    <t>ms-wor-51: {"Collapsing House": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Tzen WoR Collapsing house</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not getting mapped?  Never counted as valid b.c of forced connections.  </t>
   </si>
 </sst>
 </file>
@@ -1001,47 +1007,47 @@
         <v>0</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>44</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J4" t="s">
         <v>1</v>
@@ -1049,19 +1055,19 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J5" t="s">
         <v>2</v>
@@ -1069,16 +1075,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" s="4">
         <v>313</v>
@@ -1089,57 +1095,57 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" t="s">
-        <v>54</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F7" s="1"/>
       <c r="J7" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
         <v>56</v>
-      </c>
-      <c r="D9" t="s">
-        <v>57</v>
       </c>
       <c r="E9" s="4">
         <v>104</v>
@@ -1150,36 +1156,39 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="D11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="J11" t="s">
         <v>5</v>
@@ -1187,19 +1196,19 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="D12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="J12" t="s">
         <v>6</v>
@@ -1207,13 +1216,16 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" s="4">
         <v>532</v>
@@ -1224,16 +1236,19 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="D14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="J14" t="s">
         <v>8</v>
@@ -1241,16 +1256,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="J15" t="s">
         <v>9</v>
@@ -1258,13 +1276,16 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E16" s="4">
         <v>220</v>
@@ -1275,13 +1296,16 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E17" s="4">
         <v>151</v>
@@ -1292,553 +1316,556 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="4">
-        <v>395</v>
+        <v>70</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="J18" t="s">
-        <v>12</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" t="s">
         <v>76</v>
-      </c>
-      <c r="D21" t="s">
-        <v>77</v>
       </c>
       <c r="E21" s="4">
         <v>349</v>
       </c>
       <c r="J21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="J22" t="s">
         <v>169</v>
-      </c>
-      <c r="J22" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" t="s">
         <v>83</v>
-      </c>
-      <c r="D24" t="s">
-        <v>84</v>
       </c>
       <c r="E24" s="4">
         <v>429</v>
       </c>
       <c r="J24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E25" s="4">
         <v>193</v>
       </c>
       <c r="J25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E27" s="4">
         <v>256</v>
       </c>
       <c r="J27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" t="s">
         <v>90</v>
       </c>
-      <c r="D28" t="s">
-        <v>91</v>
-      </c>
       <c r="E28" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E32" s="4">
         <v>475</v>
       </c>
       <c r="J32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D33" t="s">
-        <v>100</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="J33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C35" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D35" t="s">
-        <v>104</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="J35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" t="s">
         <v>106</v>
       </c>
-      <c r="D37" t="s">
-        <v>107</v>
-      </c>
       <c r="E37" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" t="s">
         <v>113</v>
-      </c>
-      <c r="D40" t="s">
-        <v>114</v>
       </c>
       <c r="E40" s="4">
         <v>488</v>
       </c>
       <c r="J40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E41" s="4">
         <v>284</v>
       </c>
       <c r="J41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E42" s="4">
         <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" t="s">
         <v>116</v>
-      </c>
-      <c r="D43" t="s">
-        <v>117</v>
       </c>
       <c r="E43" s="4">
         <v>65</v>
       </c>
       <c r="J43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" t="s">
         <v>119</v>
-      </c>
-      <c r="D44" t="s">
-        <v>120</v>
       </c>
       <c r="E44" s="4">
         <v>368</v>
       </c>
       <c r="J44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C45" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45" t="s">
         <v>121</v>
-      </c>
-      <c r="D45" t="s">
-        <v>122</v>
       </c>
       <c r="E45" s="4">
         <v>363</v>
       </c>
       <c r="J45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
+        <v>122</v>
+      </c>
+      <c r="D46" t="s">
+        <v>126</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D46" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="J46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1848,7 +1875,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C8A44C-B798-4416-9AA8-07AAF9D050FB}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" style="1" customWidth="1"/>
@@ -1858,7 +1885,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E1" s="4"/>
     </row>
@@ -1867,218 +1894,232 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" t="s">
         <v>132</v>
-      </c>
-      <c r="D4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" t="s">
+        <v>135</v>
+      </c>
+      <c r="G10" t="s">
         <v>163</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D10" t="s">
-        <v>136</v>
-      </c>
-      <c r="G10" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="G11" t="s">
         <v>153</v>
-      </c>
-      <c r="G11" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" t="s">
+        <v>154</v>
+      </c>
+      <c r="G15" t="s">
         <v>156</v>
-      </c>
-      <c r="D15" t="s">
-        <v>155</v>
-      </c>
-      <c r="G15" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C16" s="4">
         <v>507</v>
       </c>
       <c r="D16" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" t="s">
         <v>160</v>
-      </c>
-      <c r="G16" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C17" s="4">
         <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>165</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="4">
+        <v>220</v>
+      </c>
+      <c r="D18" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A44EF6F-8515-4DBC-8DF7-E53DC2C2FB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507477B3-75CA-4687-92D7-84B86365B551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="19200" windowHeight="11170" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="173">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -556,9 +556,6 @@
   </si>
   <si>
     <t>ms-wor-51: {"Collapsing House": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Tzen WoR Collapsing house</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not getting mapped?  Never counted as valid b.c of forced connections.  </t>
   </si>
 </sst>
 </file>
@@ -1258,6 +1255,9 @@
       <c r="A15" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="B15" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="C15" t="s">
         <v>64</v>
       </c>
@@ -1267,9 +1267,7 @@
       <c r="E15" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>173</v>
-      </c>
+      <c r="F15" s="9"/>
       <c r="J15" t="s">
         <v>9</v>
       </c>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507477B3-75CA-4687-92D7-84B86365B551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4A3999-8708-4EA6-B5CD-5D8EF50468B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="19200" windowHeight="11170" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="174">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -556,6 +556,9 @@
   </si>
   <si>
     <t>ms-wor-51: {"Collapsing House": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Tzen WoR Collapsing house</t>
+  </si>
+  <si>
+    <t>Connection from event door --&gt; veldt used to summon airship (should be fixed).  Common culprit:  phantom train.  Also played "Searching for Friends" instead of "The Veldt"</t>
   </si>
 </sst>
 </file>
@@ -1592,6 +1595,9 @@
       <c r="A33" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="B33" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="C33" t="s">
         <v>95</v>
       </c>
@@ -1873,7 +1879,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C8A44C-B798-4416-9AA8-07AAF9D050FB}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" style="1" customWidth="1"/>
@@ -2120,6 +2126,17 @@
         <v>171</v>
       </c>
     </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" t="s">
+        <v>173</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4A3999-8708-4EA6-B5CD-5D8EF50468B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2912C01C-26D0-4CAB-B8D6-FE02809BFD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="175">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -126,9 +126,6 @@
     <t>'ruin-daryl': {"Daryl's Tomb": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Daryl's Tomb</t>
   </si>
   <si>
-    <t>'dc-75': {"Burning House": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Burning House</t>
-  </si>
-  <si>
     <t>'ms-wor-69': {"Fanatic's Tower": [RewardType.CHARACTER, RewardType.ESPER]},   # Fanatics Tower</t>
   </si>
   <si>
@@ -366,9 +363,6 @@
     <t>Ebot's Rock</t>
   </si>
   <si>
-    <t>dc-75</t>
-  </si>
-  <si>
     <t>ms-wor-69</t>
   </si>
   <si>
@@ -559,6 +553,15 @@
   </si>
   <si>
     <t>Connection from event door --&gt; veldt used to summon airship (should be fixed).  Common culprit:  phantom train.  Also played "Searching for Friends" instead of "The Veldt"</t>
+  </si>
+  <si>
+    <t>ruin-thamasa</t>
+  </si>
+  <si>
+    <t>ruin-thamasa': {"Burning House": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Burning House</t>
+  </si>
+  <si>
+    <t>Broken! burning house not randomized?</t>
   </si>
 </sst>
 </file>
@@ -1007,47 +1010,47 @@
         <v>0</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" t="s">
-        <v>43</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J4" t="s">
         <v>1</v>
@@ -1055,19 +1058,19 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J5" t="s">
         <v>2</v>
@@ -1075,16 +1078,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6" s="4">
         <v>313</v>
@@ -1095,57 +1098,57 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" t="s">
-        <v>53</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F7" s="1"/>
       <c r="J7" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
         <v>55</v>
-      </c>
-      <c r="D9" t="s">
-        <v>56</v>
       </c>
       <c r="E9" s="4">
         <v>104</v>
@@ -1156,39 +1159,39 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="D11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="J11" t="s">
         <v>5</v>
@@ -1196,19 +1199,19 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="D12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="J12" t="s">
         <v>6</v>
@@ -1216,16 +1219,16 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" s="4">
         <v>532</v>
@@ -1236,19 +1239,19 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="D14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>65</v>
       </c>
       <c r="J14" t="s">
         <v>8</v>
@@ -1256,19 +1259,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F15" s="9"/>
       <c r="J15" t="s">
@@ -1277,16 +1280,16 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" s="4">
         <v>220</v>
@@ -1297,16 +1300,16 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17" s="4">
         <v>151</v>
@@ -1317,39 +1320,39 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J19" t="s">
         <v>12</v>
@@ -1357,19 +1360,19 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J20" t="s">
         <v>13</v>
@@ -1377,16 +1380,16 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
         <v>75</v>
-      </c>
-      <c r="D21" t="s">
-        <v>76</v>
       </c>
       <c r="E21" s="4">
         <v>349</v>
@@ -1397,42 +1400,42 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J22" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J23" t="s">
         <v>15</v>
@@ -1440,13 +1443,16 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" t="s">
         <v>82</v>
-      </c>
-      <c r="D24" t="s">
-        <v>83</v>
       </c>
       <c r="E24" s="4">
         <v>429</v>
@@ -1457,13 +1463,16 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E25" s="4">
         <v>193</v>
@@ -1474,16 +1483,19 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J26" t="s">
         <v>18</v>
@@ -1491,13 +1503,16 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E27" s="4">
         <v>256</v>
@@ -1508,16 +1523,19 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" t="s">
         <v>89</v>
       </c>
-      <c r="D28" t="s">
-        <v>90</v>
-      </c>
       <c r="E28" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J28" t="s">
         <v>20</v>
@@ -1525,16 +1543,19 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J29" t="s">
         <v>21</v>
@@ -1542,16 +1563,19 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J30" t="s">
         <v>22</v>
@@ -1559,16 +1583,19 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J31" t="s">
         <v>23</v>
@@ -1576,13 +1603,16 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E32" s="4">
         <v>475</v>
@@ -1593,19 +1623,19 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="D33" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="J33" t="s">
         <v>25</v>
@@ -1613,16 +1643,19 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J34" t="s">
         <v>26</v>
@@ -1630,19 +1663,19 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="D35" t="s">
-        <v>103</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="J35" t="s">
         <v>27</v>
@@ -1650,226 +1683,226 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J36" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="C37" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" t="s">
         <v>105</v>
       </c>
-      <c r="D37" t="s">
-        <v>106</v>
-      </c>
       <c r="E37" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="J37" t="s">
-        <v>29</v>
+        <v>172</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E40" s="4">
         <v>488</v>
       </c>
       <c r="J40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C41" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" t="s">
         <v>112</v>
-      </c>
-      <c r="D41" t="s">
-        <v>114</v>
       </c>
       <c r="E41" s="4">
         <v>284</v>
       </c>
       <c r="J41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" t="s">
         <v>115</v>
-      </c>
-      <c r="D42" t="s">
-        <v>117</v>
       </c>
       <c r="E42" s="4">
         <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E43" s="4">
         <v>65</v>
       </c>
       <c r="J43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C44" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D44" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E44" s="4">
         <v>368</v>
       </c>
       <c r="J44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D45" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E45" s="4">
         <v>363</v>
       </c>
       <c r="J45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D46" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D47" t="s">
+        <v>125</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D47" t="s">
-        <v>127</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="J47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D48" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1889,7 +1922,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E1" s="4"/>
     </row>
@@ -1898,243 +1931,243 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" t="s">
         <v>131</v>
-      </c>
-      <c r="D5" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" t="s">
         <v>138</v>
       </c>
-      <c r="D14" t="s">
-        <v>140</v>
-      </c>
       <c r="G14" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D15" t="s">
+        <v>152</v>
+      </c>
+      <c r="G15" t="s">
         <v>154</v>
-      </c>
-      <c r="G15" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="4">
         <v>507</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G16" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C17" s="4">
         <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="4">
         <v>220</v>
       </c>
       <c r="D18" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2912C01C-26D0-4CAB-B8D6-FE02809BFD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B919E58-1CE6-4E62-92DD-1FFA57766E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="11170" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="173">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -555,13 +555,7 @@
     <t>Connection from event door --&gt; veldt used to summon airship (should be fixed).  Common culprit:  phantom train.  Also played "Searching for Friends" instead of "The Veldt"</t>
   </si>
   <si>
-    <t>ruin-thamasa</t>
-  </si>
-  <si>
-    <t>ruin-thamasa': {"Burning House": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Burning House</t>
-  </si>
-  <si>
-    <t>Broken! burning house not randomized?</t>
+    <t>465: {"Burning House": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Burning House</t>
   </si>
 </sst>
 </file>
@@ -1702,20 +1696,24 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="C37" t="s">
         <v>104</v>
       </c>
       <c r="D37" t="s">
         <v>105</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="4">
+        <v>465</v>
+      </c>
+      <c r="F37" s="9"/>
+      <c r="J37" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
@@ -1739,6 +1737,9 @@
       <c r="A39" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="B39" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="C39" t="s">
         <v>104</v>
       </c>
@@ -1756,6 +1757,9 @@
       <c r="A40" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="B40" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="C40" t="s">
         <v>110</v>
       </c>
@@ -1771,6 +1775,9 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C41" t="s">

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B919E58-1CE6-4E62-92DD-1FFA57766E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54341C4B-5422-43FE-8EC2-5C5B65CCED17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="11170" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54341C4B-5422-43FE-8EC2-5C5B65CCED17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3DF525-E2F6-4F8A-9CD9-5207A28A0C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="174">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -138,9 +138,6 @@
     <t>284: {"Owzer Mansion": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},   # Owzer's Basement</t>
   </si>
   <si>
-    <t>23: {"Lone Wolf": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},   # Lone Wolf.  Move to WOR?</t>
-  </si>
-  <si>
     <t>65: {"Narshe Moogle Defense": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},   # Moogle Defense WOR (need to update how this starts); 65 in WOB</t>
   </si>
   <si>
@@ -556,13 +553,19 @@
   </si>
   <si>
     <t>465: {"Burning House": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Burning House</t>
+  </si>
+  <si>
+    <t>mostly works but updates ALL characters to "MAGIC ONLY".</t>
+  </si>
+  <si>
+    <t>'41a': {"Lone Wolf": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},   # Lone Wolf.  Move to WOR?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -622,6 +625,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -643,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -656,6 +667,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1004,47 +1016,47 @@
         <v>0</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" t="s">
-        <v>42</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J4" t="s">
         <v>1</v>
@@ -1052,19 +1064,19 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J5" t="s">
         <v>2</v>
@@ -1072,16 +1084,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" s="4">
         <v>313</v>
@@ -1092,57 +1104,57 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s">
-        <v>52</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F7" s="1"/>
       <c r="J7" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
         <v>54</v>
-      </c>
-      <c r="D9" t="s">
-        <v>55</v>
       </c>
       <c r="E9" s="4">
         <v>104</v>
@@ -1153,39 +1165,39 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>163</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="D11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="J11" t="s">
         <v>5</v>
@@ -1193,19 +1205,19 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="D12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="J12" t="s">
         <v>6</v>
@@ -1213,16 +1225,16 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" s="4">
         <v>532</v>
@@ -1233,19 +1245,19 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="D14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="J14" t="s">
         <v>8</v>
@@ -1253,19 +1265,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F15" s="9"/>
       <c r="J15" t="s">
@@ -1274,16 +1286,16 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" s="4">
         <v>220</v>
@@ -1294,16 +1306,16 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" s="4">
         <v>151</v>
@@ -1314,39 +1326,39 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J19" t="s">
         <v>12</v>
@@ -1354,19 +1366,19 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J20" t="s">
         <v>13</v>
@@ -1374,16 +1386,16 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" t="s">
         <v>74</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
       </c>
       <c r="E21" s="4">
         <v>349</v>
@@ -1394,42 +1406,42 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="J22" t="s">
         <v>166</v>
-      </c>
-      <c r="J22" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J23" t="s">
         <v>15</v>
@@ -1437,16 +1449,16 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" t="s">
         <v>81</v>
-      </c>
-      <c r="D24" t="s">
-        <v>82</v>
       </c>
       <c r="E24" s="4">
         <v>429</v>
@@ -1457,16 +1469,16 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E25" s="4">
         <v>193</v>
@@ -1477,19 +1489,19 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J26" t="s">
         <v>18</v>
@@ -1497,16 +1509,16 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E27" s="4">
         <v>256</v>
@@ -1517,19 +1529,19 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" t="s">
         <v>88</v>
       </c>
-      <c r="D28" t="s">
-        <v>89</v>
-      </c>
       <c r="E28" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J28" t="s">
         <v>20</v>
@@ -1537,19 +1549,19 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J29" t="s">
         <v>21</v>
@@ -1557,19 +1569,19 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s">
         <v>22</v>
@@ -1577,19 +1589,19 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J31" t="s">
         <v>23</v>
@@ -1597,16 +1609,16 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E32" s="4">
         <v>475</v>
@@ -1617,19 +1629,19 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="D33" t="s">
-        <v>98</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="J33" t="s">
         <v>25</v>
@@ -1637,19 +1649,19 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J34" t="s">
         <v>26</v>
@@ -1657,19 +1669,19 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C35" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="D35" t="s">
-        <v>102</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="J35" t="s">
         <v>27</v>
@@ -1677,19 +1689,19 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J36" t="s">
         <v>28</v>
@@ -1697,37 +1709,40 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37" t="s">
         <v>104</v>
-      </c>
-      <c r="D37" t="s">
-        <v>105</v>
       </c>
       <c r="E37" s="4">
         <v>465</v>
       </c>
       <c r="F37" s="9"/>
       <c r="J37" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>172</v>
       </c>
       <c r="J38" t="s">
         <v>29</v>
@@ -1735,19 +1750,19 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J39" t="s">
         <v>30</v>
@@ -1755,16 +1770,16 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" t="s">
         <v>110</v>
-      </c>
-      <c r="D40" t="s">
-        <v>111</v>
       </c>
       <c r="E40" s="4">
         <v>488</v>
@@ -1775,16 +1790,16 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E41" s="4">
         <v>284</v>
@@ -1795,121 +1810,124 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D42" t="s">
-        <v>115</v>
-      </c>
-      <c r="E42" s="4">
-        <v>23</v>
-      </c>
-      <c r="J42" t="s">
-        <v>33</v>
+        <v>114</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="C43" t="s">
+        <v>112</v>
+      </c>
+      <c r="D43" t="s">
         <v>113</v>
-      </c>
-      <c r="D43" t="s">
-        <v>114</v>
       </c>
       <c r="E43" s="4">
         <v>65</v>
       </c>
       <c r="J43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C44" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" t="s">
         <v>116</v>
-      </c>
-      <c r="D44" t="s">
-        <v>117</v>
       </c>
       <c r="E44" s="4">
         <v>368</v>
       </c>
       <c r="J44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C45" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" t="s">
         <v>118</v>
-      </c>
-      <c r="D45" t="s">
-        <v>119</v>
       </c>
       <c r="E45" s="4">
         <v>363</v>
       </c>
       <c r="J45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
+        <v>119</v>
+      </c>
+      <c r="D46" t="s">
+        <v>123</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D46" t="s">
-        <v>124</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>121</v>
-      </c>
       <c r="J46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D48" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1929,7 +1947,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E1" s="4"/>
     </row>
@@ -1938,243 +1956,243 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" t="s">
         <v>129</v>
-      </c>
-      <c r="D4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G10" t="s">
         <v>160</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D10" t="s">
-        <v>133</v>
-      </c>
-      <c r="G10" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G11" t="s">
         <v>150</v>
-      </c>
-      <c r="G11" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" t="s">
+        <v>151</v>
+      </c>
+      <c r="G15" t="s">
         <v>153</v>
-      </c>
-      <c r="D15" t="s">
-        <v>152</v>
-      </c>
-      <c r="G15" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="4">
         <v>507</v>
       </c>
       <c r="D16" t="s">
+        <v>156</v>
+      </c>
+      <c r="G16" t="s">
         <v>157</v>
-      </c>
-      <c r="G16" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="4">
         <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" s="4">
         <v>220</v>
       </c>
       <c r="D18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3DF525-E2F6-4F8A-9CD9-5207A28A0C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40A1996-A4AC-4375-86C9-62C339F19EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="180">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -555,10 +555,28 @@
     <t>465: {"Burning House": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},  # Burning House</t>
   </si>
   <si>
-    <t>mostly works but updates ALL characters to "MAGIC ONLY".</t>
-  </si>
-  <si>
     <t>'41a': {"Lone Wolf": [RewardType.CHARACTER, RewardType.ESPER, RewardType.ITEM]},   # Lone Wolf.  Move to WOR?</t>
+  </si>
+  <si>
+    <t>Had to turn off y-swap while inside</t>
+  </si>
+  <si>
+    <t>Works, but need to add invisible blocker or something on umaro cave exit to prevent leaving the screen.</t>
+  </si>
+  <si>
+    <t>Works, but need to add invisible blocker or something oo umaro cave exit to prevent leaving the screen.</t>
+  </si>
+  <si>
+    <t>Works, but need to add invisible blocker or something ma umaro cave exit to prevent leaving the screen.</t>
+  </si>
+  <si>
+    <t>Works, but need to add invisible blocker or something ri umaro cave exit to prevent leaving the screen.</t>
+  </si>
+  <si>
+    <t>Works, but need to add invisible blocker or something ze umaro cave exit to prevent leaving the screen.</t>
+  </si>
+  <si>
+    <t>Works, but need to add invisible blocker or something uc umaro cave exit to prevent leaving the screen.</t>
   </si>
 </sst>
 </file>
@@ -1732,6 +1750,9 @@
       <c r="A38" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B38" s="3" t="s">
+        <v>159</v>
+      </c>
       <c r="C38" t="s">
         <v>103</v>
       </c>
@@ -1742,7 +1763,7 @@
         <v>107</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J38" t="s">
         <v>29</v>
@@ -1812,6 +1833,9 @@
       <c r="A42" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B42" s="3" t="s">
+        <v>159</v>
+      </c>
       <c r="C42" t="s">
         <v>112</v>
       </c>
@@ -1821,8 +1845,11 @@
       <c r="E42" s="4" t="s">
         <v>120</v>
       </c>
+      <c r="F42" s="10" t="s">
+        <v>174</v>
+      </c>
       <c r="J42" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40A1996-A4AC-4375-86C9-62C339F19EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EE6695-D68A-45CF-8174-C621E8ED8F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="174">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -559,24 +559,6 @@
   </si>
   <si>
     <t>Had to turn off y-swap while inside</t>
-  </si>
-  <si>
-    <t>Works, but need to add invisible blocker or something on umaro cave exit to prevent leaving the screen.</t>
-  </si>
-  <si>
-    <t>Works, but need to add invisible blocker or something oo umaro cave exit to prevent leaving the screen.</t>
-  </si>
-  <si>
-    <t>Works, but need to add invisible blocker or something ma umaro cave exit to prevent leaving the screen.</t>
-  </si>
-  <si>
-    <t>Works, but need to add invisible blocker or something ri umaro cave exit to prevent leaving the screen.</t>
-  </si>
-  <si>
-    <t>Works, but need to add invisible blocker or something ze umaro cave exit to prevent leaving the screen.</t>
-  </si>
-  <si>
-    <t>Works, but need to add invisible blocker or something uc umaro cave exit to prevent leaving the screen.</t>
   </si>
 </sst>
 </file>
@@ -1834,7 +1816,7 @@
         <v>50</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>159</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
         <v>112</v>
@@ -1845,9 +1827,7 @@
       <c r="E42" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F42" s="10" t="s">
-        <v>174</v>
-      </c>
+      <c r="F42" s="10"/>
       <c r="J42" s="7" t="s">
         <v>172</v>
       </c>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EE6695-D68A-45CF-8174-C621E8ED8F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB0FE6E-441A-49B0-BC13-6EF11865DEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="-26910" yWindow="1620" windowWidth="16305" windowHeight="15765" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB0FE6E-441A-49B0-BC13-6EF11865DEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AF2A32-0F51-4960-BA79-8F08BFCA17FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26910" yWindow="1620" windowWidth="16305" windowHeight="15765" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="174">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -1856,6 +1856,9 @@
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B44" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="C44" t="s">
         <v>115</v>
       </c>
@@ -1873,6 +1876,9 @@
       <c r="A45" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B45" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="C45" t="s">
         <v>117</v>
       </c>
@@ -1890,6 +1896,9 @@
       <c r="A46" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B46" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="C46" t="s">
         <v>119</v>
       </c>
@@ -1907,6 +1916,9 @@
       <c r="A47" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B47" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="C47" t="s">
         <v>119</v>
       </c>
@@ -1922,6 +1934,9 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C48" t="s">

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AF2A32-0F51-4960-BA79-8F08BFCA17FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532C5DD5-8AAF-44EA-A118-E8033FBCD1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" activeTab="1" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="179">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -559,6 +559,21 @@
   </si>
   <si>
     <t>Had to turn off y-swap while inside</t>
+  </si>
+  <si>
+    <t>If LOCKE not recruited, TunnelArmr should not trigger.</t>
+  </si>
+  <si>
+    <t>LOCAL CHARACTER GATING UPDATES:</t>
+  </si>
+  <si>
+    <t>If TERRA not recruited, Ultros should not trigger.</t>
+  </si>
+  <si>
+    <t>If EDGAR not recruited, cannot enter the basement.</t>
+  </si>
+  <si>
+    <t>If EDGAR not recruited, statue does nothing.</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1974,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C8A44C-B798-4416-9AA8-07AAF9D050FB}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" style="1" customWidth="1"/>
@@ -2217,6 +2232,55 @@
         <v>170</v>
       </c>
     </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="4">
+        <v>104</v>
+      </c>
+      <c r="D23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="4">
+        <v>532</v>
+      </c>
+      <c r="D25" t="s">
+        <v>178</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/claude_reference/Ruin_playtesting_checklist.xlsx
+++ b/claude_reference/Ruin_playtesting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansr\Documents\GitHub\WorldsCollide\claude_reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532C5DD5-8AAF-44EA-A118-E8033FBCD1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC1822E-7915-4CE8-855E-726EB09E48AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" activeTab="1" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{690EC4E7-DE9A-4E52-B9DA-56D934A5EC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Rewards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="179">
   <si>
     <t>PLAYTESTING CHECKLIST: Rewards in -ruin mode</t>
   </si>
@@ -2241,6 +2241,9 @@
       <c r="A22" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B22" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="C22" s="4" t="s">
         <v>47</v>
       </c>
@@ -2252,6 +2255,9 @@
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B23" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="C23" s="4">
         <v>104</v>
       </c>
@@ -2263,6 +2269,9 @@
       <c r="A24" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B24" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="C24" s="4" t="s">
         <v>58</v>
       </c>
@@ -2272,6 +2281,9 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C25" s="4">
